--- a/Tracey's Folder/Tag Returns/All Tag Returns/Connors Fish Tag Data 2024.xlsx
+++ b/Tracey's Folder/Tag Returns/All Tag Returns/Connors Fish Tag Data 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience.sharepoint.com/sites/AFF44Contract/Shared Documents/Website/2024 Returns/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Tracey's Folder\Tag Returns\All Tag Returns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1365" documentId="8_{DE61676B-7AED-41C5-BBCE-5889CDA554D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AB7EDF1-569F-46E3-885C-8C88D9DA41A4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DD40DD-8607-4BC7-A992-268C3E6A05C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="8" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5805" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5729" uniqueCount="1215">
   <si>
     <t>DATE</t>
   </si>
@@ -3576,9 +3576,6 @@
   </si>
   <si>
     <t>xxxs230823</t>
-  </si>
-  <si>
-    <t>0609123 (XX)</t>
   </si>
   <si>
     <t>070923 (XX)</t>
@@ -4232,6 +4229,12 @@
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4239,12 +4242,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4550,32 +4547,34 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="39" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="39" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="39" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" style="39" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" style="39" customWidth="1"/>
-    <col min="6" max="6" width="48" style="39" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="39" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="39" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="39" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="48" style="39" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="39" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="23" style="39" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="39" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="39" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="22.140625" style="39" customWidth="1"/>
-    <col min="11" max="11" width="28" style="39" customWidth="1"/>
+    <col min="11" max="11" width="28" style="39" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>1002</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="60" t="s">
@@ -5327,8 +5326,8 @@
       <c r="B27" s="62">
         <v>45583</v>
       </c>
-      <c r="C27" s="39" t="s">
-        <v>1046</v>
+      <c r="C27" s="61">
+        <v>45506</v>
       </c>
       <c r="D27" s="39" t="s">
         <v>639</v>
@@ -5369,7 +5368,7 @@
         <v>593</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K28" s="39" t="s">
         <v>742</v>
@@ -5401,7 +5400,7 @@
         <v>593</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K29" s="39" t="s">
         <v>732</v>
@@ -5433,7 +5432,7 @@
         <v>593</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K30" s="39" t="s">
         <v>732</v>
@@ -5468,16 +5467,16 @@
         <v>84</v>
       </c>
       <c r="K31" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L31" t="s">
         <v>1065</v>
       </c>
       <c r="O31" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P31" t="s">
         <v>1193</v>
-      </c>
-      <c r="P31" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -5506,16 +5505,16 @@
         <v>84</v>
       </c>
       <c r="K32" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L32" t="s">
         <v>1065</v>
       </c>
       <c r="O32" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P32" t="s">
         <v>1193</v>
-      </c>
-      <c r="P32" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -5544,16 +5543,16 @@
         <v>84</v>
       </c>
       <c r="K33" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L33" t="s">
         <v>1065</v>
       </c>
       <c r="O33" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P33" t="s">
         <v>1193</v>
-      </c>
-      <c r="P33" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -5582,19 +5581,19 @@
         <v>50</v>
       </c>
       <c r="K34" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L34" t="s">
         <v>1062</v>
       </c>
       <c r="O34" t="s">
+        <v>1197</v>
+      </c>
+      <c r="P34" t="s">
         <v>1198</v>
       </c>
-      <c r="P34" t="s">
-        <v>1199</v>
-      </c>
       <c r="Q34" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5623,19 +5622,19 @@
         <v>50</v>
       </c>
       <c r="K35" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L35" t="s">
         <v>1062</v>
       </c>
       <c r="O35" t="s">
+        <v>1197</v>
+      </c>
+      <c r="P35" t="s">
         <v>1198</v>
       </c>
-      <c r="P35" t="s">
-        <v>1199</v>
-      </c>
       <c r="Q35" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -5664,16 +5663,16 @@
         <v>84</v>
       </c>
       <c r="K36" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L36" t="s">
         <v>1065</v>
       </c>
       <c r="O36" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P36" t="s">
         <v>1193</v>
-      </c>
-      <c r="P36" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -5702,16 +5701,16 @@
         <v>84</v>
       </c>
       <c r="K37" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L37" t="s">
         <v>1065</v>
       </c>
       <c r="O37" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P37" t="s">
         <v>1193</v>
-      </c>
-      <c r="P37" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -5740,16 +5739,16 @@
         <v>171</v>
       </c>
       <c r="K38" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L38" t="s">
         <v>1066</v>
       </c>
       <c r="O38" t="s">
+        <v>1199</v>
+      </c>
+      <c r="P38" t="s">
         <v>1200</v>
-      </c>
-      <c r="P38" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -5760,7 +5759,7 @@
         <v>45378</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D39" s="39" t="s">
         <v>817</v>
@@ -5769,7 +5768,7 @@
         <v>1067</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="I39" s="39" t="s">
         <v>593</v>
@@ -5804,16 +5803,16 @@
         <v>108</v>
       </c>
       <c r="K40" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L40" t="s">
         <v>1069</v>
       </c>
       <c r="O40" t="s">
+        <v>1202</v>
+      </c>
+      <c r="P40" t="s">
         <v>1203</v>
-      </c>
-      <c r="P40" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -5842,16 +5841,16 @@
         <v>185</v>
       </c>
       <c r="K41" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L41" t="s">
         <v>1070</v>
       </c>
       <c r="O41" t="s">
+        <v>1204</v>
+      </c>
+      <c r="P41" t="s">
         <v>1205</v>
-      </c>
-      <c r="P41" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -5862,7 +5861,7 @@
         <v>45372</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D42" s="39" t="s">
         <v>794</v>
@@ -5900,7 +5899,7 @@
         <v>593</v>
       </c>
       <c r="J43" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K43" s="39" t="s">
         <v>742</v>
@@ -5932,7 +5931,7 @@
         <v>593</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K44" s="39" t="s">
         <v>742</v>
@@ -5964,7 +5963,7 @@
         <v>593</v>
       </c>
       <c r="J45" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K45" s="39" t="s">
         <v>742</v>
@@ -5996,7 +5995,7 @@
         <v>593</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K46" s="39" t="s">
         <v>742</v>
@@ -6028,7 +6027,7 @@
         <v>593</v>
       </c>
       <c r="J47" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K47" s="39" t="s">
         <v>742</v>
@@ -6060,7 +6059,7 @@
         <v>593</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K48" s="39" t="s">
         <v>742</v>
@@ -6095,16 +6094,16 @@
         <v>50</v>
       </c>
       <c r="K49" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L49" t="s">
         <v>1062</v>
       </c>
       <c r="O49" t="s">
+        <v>1197</v>
+      </c>
+      <c r="P49" t="s">
         <v>1198</v>
-      </c>
-      <c r="P49" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -6133,16 +6132,16 @@
         <v>50</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L50" t="s">
         <v>1062</v>
       </c>
       <c r="O50" t="s">
+        <v>1197</v>
+      </c>
+      <c r="P50" t="s">
         <v>1198</v>
-      </c>
-      <c r="P50" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -6171,16 +6170,16 @@
         <v>50</v>
       </c>
       <c r="K51" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L51" t="s">
         <v>1062</v>
       </c>
       <c r="O51" t="s">
+        <v>1197</v>
+      </c>
+      <c r="P51" t="s">
         <v>1198</v>
-      </c>
-      <c r="P51" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -6209,16 +6208,16 @@
         <v>50</v>
       </c>
       <c r="K52" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L52" t="s">
         <v>1062</v>
       </c>
       <c r="O52" t="s">
+        <v>1197</v>
+      </c>
+      <c r="P52" t="s">
         <v>1198</v>
-      </c>
-      <c r="P52" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -6244,7 +6243,7 @@
         <v>593</v>
       </c>
       <c r="J53" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K53" s="39" t="s">
         <v>742</v>
@@ -6279,7 +6278,7 @@
         <v>50</v>
       </c>
       <c r="K54" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L54" t="s">
         <v>1079</v>
@@ -6311,7 +6310,7 @@
         <v>50</v>
       </c>
       <c r="K55" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L55" t="s">
         <v>1079</v>
@@ -6343,7 +6342,7 @@
         <v>50</v>
       </c>
       <c r="K56" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L56" t="s">
         <v>1079</v>
@@ -6375,7 +6374,7 @@
         <v>50</v>
       </c>
       <c r="K57" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L57" t="s">
         <v>1079</v>
@@ -6430,7 +6429,7 @@
         <v>50</v>
       </c>
       <c r="K59" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L59" t="s">
         <v>1084</v>
@@ -6462,7 +6461,7 @@
         <v>50</v>
       </c>
       <c r="K60" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L60" t="s">
         <v>1079</v>
@@ -6494,7 +6493,7 @@
         <v>50</v>
       </c>
       <c r="K61" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L61" t="s">
         <v>1079</v>
@@ -6526,7 +6525,7 @@
         <v>50</v>
       </c>
       <c r="K62" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L62" t="s">
         <v>1088</v>
@@ -6549,7 +6548,7 @@
         <v>1052</v>
       </c>
       <c r="H63" s="39" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="I63" s="39" t="s">
         <v>593</v>
@@ -6558,16 +6557,16 @@
         <v>69</v>
       </c>
       <c r="K63" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L63" t="s">
         <v>1092</v>
       </c>
       <c r="O63" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P63" t="s">
         <v>1208</v>
-      </c>
-      <c r="P63" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -6587,7 +6586,7 @@
         <v>1091</v>
       </c>
       <c r="H64" s="39" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="I64" s="39" t="s">
         <v>593</v>
@@ -6596,16 +6595,16 @@
         <v>69</v>
       </c>
       <c r="K64" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L64" t="s">
         <v>1092</v>
       </c>
       <c r="O64" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P64" t="s">
         <v>1208</v>
-      </c>
-      <c r="P64" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
@@ -6625,7 +6624,7 @@
         <v>1052</v>
       </c>
       <c r="H65" s="39" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="I65" s="39" t="s">
         <v>593</v>
@@ -6634,16 +6633,16 @@
         <v>69</v>
       </c>
       <c r="K65" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L65" t="s">
         <v>1092</v>
       </c>
       <c r="O65" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P65" t="s">
         <v>1208</v>
-      </c>
-      <c r="P65" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
@@ -6663,7 +6662,7 @@
         <v>1095</v>
       </c>
       <c r="H66" s="39" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="I66" s="39" t="s">
         <v>593</v>
@@ -6672,16 +6671,16 @@
         <v>69</v>
       </c>
       <c r="K66" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L66" t="s">
         <v>1092</v>
       </c>
       <c r="O66" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P66" t="s">
         <v>1208</v>
-      </c>
-      <c r="P66" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
@@ -6701,7 +6700,7 @@
         <v>1087</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="I67" s="39" t="s">
         <v>593</v>
@@ -6710,16 +6709,16 @@
         <v>69</v>
       </c>
       <c r="K67" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L67" t="s">
         <v>1092</v>
       </c>
       <c r="O67" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P67" t="s">
         <v>1208</v>
-      </c>
-      <c r="P67" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
@@ -6739,7 +6738,7 @@
         <v>1091</v>
       </c>
       <c r="H68" s="39" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="I68" s="39" t="s">
         <v>593</v>
@@ -6748,16 +6747,16 @@
         <v>69</v>
       </c>
       <c r="K68" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L68" t="s">
         <v>1092</v>
       </c>
       <c r="O68" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P68" t="s">
         <v>1208</v>
-      </c>
-      <c r="P68" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -6792,10 +6791,10 @@
         <v>1098</v>
       </c>
       <c r="O69" t="s">
+        <v>1209</v>
+      </c>
+      <c r="P69" t="s">
         <v>1210</v>
-      </c>
-      <c r="P69" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
@@ -6888,16 +6887,16 @@
         <v>136</v>
       </c>
       <c r="K72" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L72" t="s">
         <v>1104</v>
       </c>
       <c r="O72" t="s">
+        <v>1211</v>
+      </c>
+      <c r="P72" t="s">
         <v>1212</v>
-      </c>
-      <c r="P72" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
@@ -6932,10 +6931,10 @@
         <v>1105</v>
       </c>
       <c r="O73" t="s">
+        <v>1213</v>
+      </c>
+      <c r="P73" t="s">
         <v>1214</v>
-      </c>
-      <c r="P73" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
@@ -6964,16 +6963,16 @@
         <v>171</v>
       </c>
       <c r="K74" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L74" t="s">
         <v>1108</v>
       </c>
       <c r="O74" t="s">
+        <v>1199</v>
+      </c>
+      <c r="P74" t="s">
         <v>1200</v>
-      </c>
-      <c r="P74" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
@@ -7328,8 +7327,8 @@
       <c r="B90" s="62">
         <v>45295</v>
       </c>
-      <c r="C90" s="39" t="s">
-        <v>1046</v>
+      <c r="C90" s="61">
+        <v>45167</v>
       </c>
       <c r="D90" s="39" t="s">
         <v>902</v>
@@ -7351,8 +7350,8 @@
       <c r="B91" s="62">
         <v>45294</v>
       </c>
-      <c r="C91" s="39" t="s">
-        <v>1046</v>
+      <c r="C91" s="61">
+        <v>45175</v>
       </c>
       <c r="D91" s="58">
         <v>0.3923611111111111</v>
@@ -7374,8 +7373,8 @@
       <c r="B92" s="62">
         <v>45272</v>
       </c>
-      <c r="C92" s="39" t="s">
-        <v>1046</v>
+      <c r="C92" s="61">
+        <v>44823</v>
       </c>
       <c r="D92" s="39" t="s">
         <v>717</v>
@@ -7397,8 +7396,8 @@
       <c r="B93" s="62">
         <v>45272</v>
       </c>
-      <c r="C93" s="39" t="s">
-        <v>1046</v>
+      <c r="C93" s="61">
+        <v>45184</v>
       </c>
       <c r="D93" s="39" t="s">
         <v>894</v>
@@ -7420,8 +7419,8 @@
       <c r="B94" s="62">
         <v>45272</v>
       </c>
-      <c r="C94" s="39" t="s">
-        <v>1046</v>
+      <c r="C94" s="61">
+        <v>45161</v>
       </c>
       <c r="D94" s="39" t="s">
         <v>770</v>
@@ -7443,8 +7442,8 @@
       <c r="B95" s="62">
         <v>45272</v>
       </c>
-      <c r="C95" s="39" t="s">
-        <v>1046</v>
+      <c r="C95" s="61">
+        <v>45176</v>
       </c>
       <c r="D95" s="58">
         <v>0.39930555555555558</v>
@@ -7466,8 +7465,8 @@
       <c r="B96" s="62">
         <v>45272</v>
       </c>
-      <c r="C96" s="39" t="s">
-        <v>1046</v>
+      <c r="C96" s="61">
+        <v>44803</v>
       </c>
       <c r="D96" s="39" t="s">
         <v>817</v>
@@ -7489,8 +7488,8 @@
       <c r="B97" s="62">
         <v>45272</v>
       </c>
-      <c r="C97" s="39" t="s">
-        <v>1046</v>
+      <c r="C97" s="61">
+        <v>44823</v>
       </c>
       <c r="D97" s="58">
         <v>0.44791666666666669</v>
@@ -7512,8 +7511,8 @@
       <c r="B98" s="62">
         <v>45247</v>
       </c>
-      <c r="C98" s="39" t="s">
-        <v>1046</v>
+      <c r="C98" s="61">
+        <v>45177</v>
       </c>
       <c r="D98" s="58">
         <v>0.44791666666666669</v>
@@ -7535,8 +7534,8 @@
       <c r="B99" s="62">
         <v>45247</v>
       </c>
-      <c r="C99" s="39" t="s">
-        <v>1046</v>
+      <c r="C99" s="61">
+        <v>45176</v>
       </c>
       <c r="D99" s="39" t="s">
         <v>1137</v>
@@ -7558,8 +7557,8 @@
       <c r="B100" s="62">
         <v>45247</v>
       </c>
-      <c r="C100" s="39" t="s">
-        <v>1046</v>
+      <c r="C100" s="61">
+        <v>45176</v>
       </c>
       <c r="D100" s="39" t="s">
         <v>717</v>
@@ -7581,8 +7580,8 @@
       <c r="B101" s="62">
         <v>45247</v>
       </c>
-      <c r="C101" s="39" t="s">
-        <v>1046</v>
+      <c r="C101" s="61">
+        <v>45176</v>
       </c>
       <c r="D101" s="39" t="s">
         <v>777</v>
@@ -7604,8 +7603,8 @@
       <c r="B102" s="62">
         <v>45250</v>
       </c>
-      <c r="C102" s="39" t="s">
-        <v>1046</v>
+      <c r="C102" s="61">
+        <v>45176</v>
       </c>
       <c r="D102" s="58" t="s">
         <v>1137</v>
@@ -7627,8 +7626,8 @@
       <c r="B103" s="62">
         <v>45250</v>
       </c>
-      <c r="C103" s="39" t="s">
-        <v>1046</v>
+      <c r="C103" s="61">
+        <v>45176</v>
       </c>
       <c r="D103" s="39" t="s">
         <v>1140</v>
@@ -7650,8 +7649,8 @@
       <c r="B104" s="62">
         <v>45251</v>
       </c>
-      <c r="C104" s="39" t="s">
-        <v>1046</v>
+      <c r="C104" s="61">
+        <v>44803</v>
       </c>
       <c r="D104" s="39" t="s">
         <v>793</v>
@@ -7673,8 +7672,8 @@
       <c r="B105" s="62">
         <v>45251</v>
       </c>
-      <c r="C105" s="39" t="s">
-        <v>1046</v>
+      <c r="C105" s="61">
+        <v>44803</v>
       </c>
       <c r="D105" s="39" t="s">
         <v>603</v>
@@ -7696,8 +7695,8 @@
       <c r="B106" s="62">
         <v>45251</v>
       </c>
-      <c r="C106" s="39" t="s">
-        <v>1046</v>
+      <c r="C106" s="61">
+        <v>44803</v>
       </c>
       <c r="D106" s="39" t="s">
         <v>835</v>
@@ -7719,8 +7718,8 @@
       <c r="B107" s="62">
         <v>45251</v>
       </c>
-      <c r="C107" s="39" t="s">
-        <v>1046</v>
+      <c r="C107" s="61">
+        <v>44803</v>
       </c>
       <c r="D107" s="39" t="s">
         <v>635</v>
@@ -7742,8 +7741,8 @@
       <c r="B108" s="62">
         <v>45252</v>
       </c>
-      <c r="C108" s="39" t="s">
-        <v>1046</v>
+      <c r="C108" s="61">
+        <v>45161</v>
       </c>
       <c r="D108" s="39" t="s">
         <v>674</v>
@@ -7765,8 +7764,8 @@
       <c r="B109" s="62">
         <v>45253</v>
       </c>
-      <c r="C109" s="39" t="s">
-        <v>1046</v>
+      <c r="C109" s="61">
+        <v>45161</v>
       </c>
       <c r="D109" s="39" t="s">
         <v>770</v>
@@ -7788,8 +7787,8 @@
       <c r="B110" s="62">
         <v>45253</v>
       </c>
-      <c r="C110" s="39" t="s">
-        <v>1046</v>
+      <c r="C110" s="61">
+        <v>45161</v>
       </c>
       <c r="D110" s="39" t="s">
         <v>794</v>
@@ -7811,8 +7810,8 @@
       <c r="B111" s="62">
         <v>45253</v>
       </c>
-      <c r="C111" s="39" t="s">
-        <v>1046</v>
+      <c r="C111" s="61">
+        <v>45161</v>
       </c>
       <c r="D111" s="39" t="s">
         <v>635</v>
@@ -7834,8 +7833,8 @@
       <c r="B112" s="62">
         <v>45257</v>
       </c>
-      <c r="C112" s="39" t="s">
-        <v>1046</v>
+      <c r="C112" s="61">
+        <v>45166</v>
       </c>
       <c r="D112" s="39" t="s">
         <v>658</v>
@@ -7857,8 +7856,8 @@
       <c r="B113" s="62">
         <v>45258</v>
       </c>
-      <c r="C113" s="39" t="s">
-        <v>1046</v>
+      <c r="C113" s="61">
+        <v>45166</v>
       </c>
       <c r="D113" s="39" t="s">
         <v>1149</v>
@@ -7880,8 +7879,8 @@
       <c r="B114" s="62">
         <v>45250</v>
       </c>
-      <c r="C114" s="39" t="s">
-        <v>1046</v>
+      <c r="C114" s="61">
+        <v>45176</v>
       </c>
       <c r="D114" s="58" t="s">
         <v>608</v>
@@ -7903,8 +7902,8 @@
       <c r="B115" s="62">
         <v>45250</v>
       </c>
-      <c r="C115" s="39" t="s">
-        <v>1046</v>
+      <c r="C115" s="61">
+        <v>45176</v>
       </c>
       <c r="D115" s="39" t="s">
         <v>1152</v>
@@ -7926,8 +7925,8 @@
       <c r="B116" s="62">
         <v>45250</v>
       </c>
-      <c r="C116" s="39" t="s">
-        <v>1046</v>
+      <c r="C116" s="61">
+        <v>45176</v>
       </c>
       <c r="D116" s="39" t="s">
         <v>976</v>
@@ -7949,8 +7948,8 @@
       <c r="B117" s="62">
         <v>45250</v>
       </c>
-      <c r="C117" s="39" t="s">
-        <v>1046</v>
+      <c r="C117" s="61">
+        <v>45188</v>
       </c>
       <c r="D117" s="39" t="s">
         <v>818</v>
@@ -7972,8 +7971,8 @@
       <c r="B118" s="62">
         <v>45250</v>
       </c>
-      <c r="C118" s="39" t="s">
-        <v>1046</v>
+      <c r="C118" s="61">
+        <v>45176</v>
       </c>
       <c r="D118" s="39" t="s">
         <v>1154</v>
@@ -7995,8 +7994,8 @@
       <c r="B119" s="62">
         <v>45250</v>
       </c>
-      <c r="C119" s="39" t="s">
-        <v>1046</v>
+      <c r="C119" s="61">
+        <v>45176</v>
       </c>
       <c r="D119" s="39" t="s">
         <v>781</v>
@@ -8018,8 +8017,8 @@
       <c r="B120" s="62">
         <v>45250</v>
       </c>
-      <c r="C120" s="39" t="s">
-        <v>1046</v>
+      <c r="C120" s="61">
+        <v>45176</v>
       </c>
       <c r="D120" s="39" t="s">
         <v>1154</v>
@@ -8041,8 +8040,8 @@
       <c r="B121" s="62">
         <v>45247</v>
       </c>
-      <c r="C121" s="39" t="s">
-        <v>1046</v>
+      <c r="C121" s="61">
+        <v>45177</v>
       </c>
       <c r="D121" s="39" t="s">
         <v>1155</v>
@@ -8064,8 +8063,8 @@
       <c r="B122" s="62">
         <v>45247</v>
       </c>
-      <c r="C122" s="39" t="s">
-        <v>1046</v>
+      <c r="C122" s="61">
+        <v>45177</v>
       </c>
       <c r="D122" s="39" t="s">
         <v>608</v>
@@ -8087,8 +8086,8 @@
       <c r="B123" s="62">
         <v>45247</v>
       </c>
-      <c r="C123" s="39" t="s">
-        <v>1046</v>
+      <c r="C123" s="61">
+        <v>45177</v>
       </c>
       <c r="D123" s="39" t="s">
         <v>750</v>
@@ -8110,8 +8109,8 @@
       <c r="B124" s="62">
         <v>45247</v>
       </c>
-      <c r="C124" s="39" t="s">
-        <v>1046</v>
+      <c r="C124" s="61">
+        <v>45177</v>
       </c>
       <c r="D124" s="39" t="s">
         <v>917</v>
@@ -8133,8 +8132,8 @@
       <c r="B125" s="62">
         <v>45247</v>
       </c>
-      <c r="C125" s="39" t="s">
-        <v>1046</v>
+      <c r="C125" s="61">
+        <v>45176</v>
       </c>
       <c r="D125" s="39" t="s">
         <v>1160</v>
@@ -8156,8 +8155,8 @@
       <c r="B126" s="62">
         <v>45247</v>
       </c>
-      <c r="C126" s="39" t="s">
-        <v>1046</v>
+      <c r="C126" s="61">
+        <v>45177</v>
       </c>
       <c r="D126" s="39" t="s">
         <v>869</v>
@@ -8179,8 +8178,8 @@
       <c r="B127" s="62">
         <v>45251</v>
       </c>
-      <c r="C127" s="39" t="s">
-        <v>1046</v>
+      <c r="C127" s="61">
+        <v>44804</v>
       </c>
       <c r="D127" s="39" t="s">
         <v>739</v>
@@ -8202,8 +8201,8 @@
       <c r="B128" s="62">
         <v>45252</v>
       </c>
-      <c r="C128" s="39" t="s">
-        <v>1046</v>
+      <c r="C128" s="61">
+        <v>45180</v>
       </c>
       <c r="D128" s="39" t="s">
         <v>1152</v>
@@ -8225,8 +8224,8 @@
       <c r="B129" s="62">
         <v>45252</v>
       </c>
-      <c r="C129" s="39" t="s">
-        <v>1046</v>
+      <c r="C129" s="61">
+        <v>45176</v>
       </c>
       <c r="D129" s="39" t="s">
         <v>1166</v>
@@ -8248,8 +8247,8 @@
       <c r="B130" s="62">
         <v>45252</v>
       </c>
-      <c r="C130" s="39" t="s">
-        <v>1046</v>
+      <c r="C130" s="61">
+        <v>45194</v>
       </c>
       <c r="D130" s="39" t="s">
         <v>665</v>
@@ -8271,8 +8270,8 @@
       <c r="B131" s="62">
         <v>45252</v>
       </c>
-      <c r="C131" s="39" t="s">
-        <v>1046</v>
+      <c r="C131" s="61">
+        <v>45194</v>
       </c>
       <c r="D131" s="39" t="s">
         <v>1169</v>
@@ -8294,8 +8293,8 @@
       <c r="B132" s="62">
         <v>45252</v>
       </c>
-      <c r="C132" s="39" t="s">
-        <v>1046</v>
+      <c r="C132" s="61">
+        <v>45197</v>
       </c>
       <c r="D132" s="58" t="s">
         <v>1121</v>
@@ -8317,8 +8316,8 @@
       <c r="B133" s="62">
         <v>45247</v>
       </c>
-      <c r="C133" s="39" t="s">
-        <v>1046</v>
+      <c r="C133" s="61">
+        <v>45176</v>
       </c>
       <c r="D133" s="39" t="s">
         <v>1121</v>
@@ -8340,8 +8339,8 @@
       <c r="B134" s="62">
         <v>45247</v>
       </c>
-      <c r="C134" s="39" t="s">
-        <v>1046</v>
+      <c r="C134" s="61">
+        <v>45167</v>
       </c>
       <c r="D134" s="39" t="s">
         <v>602</v>
@@ -8363,8 +8362,8 @@
       <c r="B135" s="62">
         <v>45250</v>
       </c>
-      <c r="C135" s="39" t="s">
-        <v>1046</v>
+      <c r="C135" s="61">
+        <v>45177</v>
       </c>
       <c r="D135" s="39" t="s">
         <v>816</v>
@@ -8386,8 +8385,8 @@
       <c r="B136" s="62">
         <v>45247</v>
       </c>
-      <c r="C136" s="39" t="s">
-        <v>1046</v>
+      <c r="C136" s="61">
+        <v>45167</v>
       </c>
       <c r="D136" s="39" t="s">
         <v>1149</v>
@@ -8409,8 +8408,8 @@
       <c r="B137" s="62">
         <v>45232</v>
       </c>
-      <c r="C137" s="39" t="s">
-        <v>1046</v>
+      <c r="C137" s="61">
+        <v>45167</v>
       </c>
       <c r="D137" s="39" t="s">
         <v>812</v>
@@ -8432,8 +8431,8 @@
       <c r="B138" s="62">
         <v>45247</v>
       </c>
-      <c r="C138" s="39" t="s">
-        <v>1046</v>
+      <c r="C138" s="61">
+        <v>45175</v>
       </c>
       <c r="D138" s="39" t="s">
         <v>665</v>
@@ -8461,8 +8460,8 @@
       <c r="B139" s="62">
         <v>45244</v>
       </c>
-      <c r="C139" s="39" t="s">
-        <v>1046</v>
+      <c r="C139" s="61">
+        <v>45161</v>
       </c>
       <c r="D139" s="39" t="s">
         <v>665</v>
@@ -8484,8 +8483,8 @@
       <c r="B140" s="62">
         <v>45243</v>
       </c>
-      <c r="C140" s="39" t="s">
-        <v>1046</v>
+      <c r="C140" s="61">
+        <v>45161</v>
       </c>
       <c r="D140" s="39" t="s">
         <v>613</v>
@@ -8507,8 +8506,8 @@
       <c r="B141" s="62">
         <v>45237</v>
       </c>
-      <c r="C141" s="39" t="s">
-        <v>1046</v>
+      <c r="C141" s="61">
+        <v>45188</v>
       </c>
       <c r="D141" s="39" t="s">
         <v>736</v>
@@ -8530,8 +8529,8 @@
       <c r="B142" s="62">
         <v>45232</v>
       </c>
-      <c r="C142" s="39" t="s">
-        <v>1046</v>
+      <c r="C142" s="61">
+        <v>45167</v>
       </c>
       <c r="D142" s="39" t="s">
         <v>684</v>
@@ -8553,8 +8552,8 @@
       <c r="B143" s="62">
         <v>45246</v>
       </c>
-      <c r="C143" s="39" t="s">
-        <v>1046</v>
+      <c r="C143" s="61">
+        <v>45175</v>
       </c>
       <c r="D143" s="39" t="s">
         <v>818</v>
@@ -8566,7 +8565,7 @@
         <v>593</v>
       </c>
       <c r="L143" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="M143" t="s">
         <v>1176</v>
@@ -8579,8 +8578,8 @@
       <c r="B144" s="62">
         <v>45246</v>
       </c>
-      <c r="C144" s="39" t="s">
-        <v>1046</v>
+      <c r="C144" s="61">
+        <v>45176</v>
       </c>
       <c r="D144" s="39" t="s">
         <v>635</v>
@@ -8592,7 +8591,7 @@
         <v>593</v>
       </c>
       <c r="L144" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M144" t="s">
         <v>1176</v>
@@ -8605,20 +8604,20 @@
       <c r="B145" s="62">
         <v>45243</v>
       </c>
-      <c r="C145" s="39" t="s">
-        <v>1046</v>
+      <c r="C145" s="61">
+        <v>45161</v>
       </c>
       <c r="D145" s="39" t="s">
         <v>654</v>
       </c>
       <c r="E145" s="39" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="I145" s="39" t="s">
         <v>593</v>
       </c>
       <c r="L145">
-        <v>230523</v>
+        <v>230823</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
@@ -8628,14 +8627,14 @@
       <c r="B146" s="62">
         <v>45245</v>
       </c>
-      <c r="C146" s="39" t="s">
-        <v>1046</v>
+      <c r="C146" s="61">
+        <v>45161</v>
       </c>
       <c r="D146" s="39" t="s">
         <v>658</v>
       </c>
       <c r="E146" s="39" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="I146" s="39" t="s">
         <v>593</v>
@@ -8651,8 +8650,8 @@
       <c r="B147" s="62">
         <v>45243</v>
       </c>
-      <c r="C147" s="39" t="s">
-        <v>1046</v>
+      <c r="C147" s="61">
+        <v>45161</v>
       </c>
       <c r="D147" s="39" t="s">
         <v>817</v>
@@ -8674,8 +8673,8 @@
       <c r="B148" s="62">
         <v>45243</v>
       </c>
-      <c r="C148" s="39" t="s">
-        <v>1046</v>
+      <c r="C148" s="61">
+        <v>45161</v>
       </c>
       <c r="D148" s="39" t="s">
         <v>746</v>
@@ -8697,8 +8696,8 @@
       <c r="B149" s="62">
         <v>45243</v>
       </c>
-      <c r="C149" s="39" t="s">
-        <v>1046</v>
+      <c r="C149" s="61">
+        <v>45161</v>
       </c>
       <c r="D149" s="39" t="s">
         <v>613</v>
@@ -8720,14 +8719,14 @@
       <c r="B150" s="62">
         <v>45243</v>
       </c>
-      <c r="C150" s="39" t="s">
-        <v>1046</v>
+      <c r="C150" s="61">
+        <v>45161</v>
       </c>
       <c r="D150" s="39" t="s">
         <v>894</v>
       </c>
       <c r="E150" s="39" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I150" s="39" t="s">
         <v>593</v>
@@ -8743,8 +8742,8 @@
       <c r="B151" s="62">
         <v>45247</v>
       </c>
-      <c r="C151" s="39" t="s">
-        <v>1046</v>
+      <c r="C151" s="61">
+        <v>45175</v>
       </c>
       <c r="D151" s="39" t="s">
         <v>893</v>
@@ -8766,11 +8765,11 @@
       <c r="A152" s="39">
         <v>577946</v>
       </c>
-      <c r="B152" s="62" t="s">
-        <v>486</v>
-      </c>
-      <c r="C152" s="39" t="s">
-        <v>1046</v>
+      <c r="B152" s="62">
+        <v>45239</v>
+      </c>
+      <c r="C152" s="61">
+        <v>45184</v>
       </c>
       <c r="D152" s="39" t="s">
         <v>486</v>
@@ -8792,8 +8791,8 @@
       <c r="B153" s="62">
         <v>45239</v>
       </c>
-      <c r="C153" s="39" t="s">
-        <v>1046</v>
+      <c r="C153" s="61">
+        <v>45184</v>
       </c>
       <c r="D153" s="39" t="s">
         <v>1005</v>
@@ -8805,7 +8804,7 @@
         <v>593</v>
       </c>
       <c r="L153" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
@@ -8815,8 +8814,8 @@
       <c r="B154" s="62">
         <v>45239</v>
       </c>
-      <c r="C154" s="39" t="s">
-        <v>1046</v>
+      <c r="C154" s="61">
+        <v>45184</v>
       </c>
       <c r="D154" s="39" t="s">
         <v>1000</v>
@@ -8828,7 +8827,7 @@
         <v>593</v>
       </c>
       <c r="L154" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
@@ -8838,8 +8837,8 @@
       <c r="B155" s="62">
         <v>45238</v>
       </c>
-      <c r="C155" s="39" t="s">
-        <v>1046</v>
+      <c r="C155" s="61">
+        <v>45184</v>
       </c>
       <c r="D155" s="39" t="s">
         <v>894</v>
@@ -8861,11 +8860,11 @@
       <c r="B156" s="62">
         <v>45238</v>
       </c>
-      <c r="C156" s="39" t="s">
-        <v>1046</v>
+      <c r="C156" s="61">
+        <v>45176</v>
       </c>
       <c r="D156" s="39" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E156" s="39" t="s">
         <v>1010</v>
@@ -8874,7 +8873,7 @@
         <v>593</v>
       </c>
       <c r="L156" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="M156" t="s">
         <v>1176</v>
@@ -8887,8 +8886,8 @@
       <c r="B157" s="62">
         <v>45238</v>
       </c>
-      <c r="C157" s="39" t="s">
-        <v>1046</v>
+      <c r="C157" s="61">
+        <v>45184</v>
       </c>
       <c r="D157" s="39" t="s">
         <v>658</v>
@@ -8910,11 +8909,11 @@
       <c r="B158" s="62">
         <v>45238</v>
       </c>
-      <c r="C158" s="39" t="s">
-        <v>1046</v>
+      <c r="C158" s="61">
+        <v>45176</v>
       </c>
       <c r="D158" s="39" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E158" s="39" t="s">
         <v>1010</v>
@@ -8923,7 +8922,7 @@
         <v>593</v>
       </c>
       <c r="L158" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M158" t="s">
         <v>1176</v>
@@ -8936,8 +8935,8 @@
       <c r="B159" s="62">
         <v>45238</v>
       </c>
-      <c r="C159" s="39" t="s">
-        <v>1046</v>
+      <c r="C159" s="61">
+        <v>45184</v>
       </c>
       <c r="D159" s="39" t="s">
         <v>955</v>
@@ -8959,11 +8958,11 @@
       <c r="B160" s="62">
         <v>45238</v>
       </c>
-      <c r="C160" s="39" t="s">
-        <v>1046</v>
+      <c r="C160" s="61">
+        <v>45176</v>
       </c>
       <c r="D160" s="39" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E160" s="39" t="s">
         <v>1150</v>
@@ -8972,7 +8971,7 @@
         <v>593</v>
       </c>
       <c r="L160" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M160" t="s">
         <v>1176</v>
@@ -8985,8 +8984,8 @@
       <c r="B161" s="62">
         <v>45238</v>
       </c>
-      <c r="C161" s="39" t="s">
-        <v>1046</v>
+      <c r="C161" s="61">
+        <v>45176</v>
       </c>
       <c r="D161" s="39" t="s">
         <v>1154</v>
@@ -8998,7 +8997,7 @@
         <v>593</v>
       </c>
       <c r="L161" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M161" t="s">
         <v>1176</v>
@@ -9011,11 +9010,11 @@
       <c r="B162" s="62">
         <v>45238</v>
       </c>
-      <c r="C162" s="39" t="s">
-        <v>1046</v>
+      <c r="C162" s="61">
+        <v>45175</v>
       </c>
       <c r="D162" s="39" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E162" s="39" t="s">
         <v>1150</v>
@@ -9024,7 +9023,7 @@
         <v>593</v>
       </c>
       <c r="L162" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="M162" t="s">
         <v>1176</v>
@@ -9037,8 +9036,8 @@
       <c r="B163" s="62">
         <v>45238</v>
       </c>
-      <c r="C163" s="39" t="s">
-        <v>1046</v>
+      <c r="C163" s="61">
+        <v>45175</v>
       </c>
       <c r="D163" s="39" t="s">
         <v>893</v>
@@ -9086,19 +9085,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="65" t="s">
         <v>587</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="67"/>
     </row>
     <row r="2" spans="1:11" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
@@ -30596,15 +30595,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="aa15ca5b-4450-4fec-8212-75ae51eef6c9">
@@ -30613,6 +30603,15 @@
     <TaxCatchAll xmlns="9b77705d-b477-4602-ae15-a5316c12e631" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30635,14 +30634,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77043088-EBE2-4231-BB0C-EDD565434295}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -30651,4 +30642,12 @@
     <ds:schemaRef ds:uri="9b77705d-b477-4602-ae15-a5316c12e631"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Tracey's Folder/Tag Returns/All Tag Returns/Connors Fish Tag Data 2024.xlsx
+++ b/Tracey's Folder/Tag Returns/All Tag Returns/Connors Fish Tag Data 2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Tracey's Folder\Tag Returns\All Tag Returns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DD40DD-8607-4BC7-A992-268C3E6A05C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01C5583-8C47-45EB-8BF6-716909BC2229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4069,7 +4069,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4221,13 +4221,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4261,6 +4259,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4547,8 +4548,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="39" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="39" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="39" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="39" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" style="60" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" style="39" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="28.42578125" style="39" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="48" style="39" hidden="1" customWidth="1"/>
@@ -4556,58 +4557,58 @@
     <col min="8" max="8" width="23" style="39" customWidth="1"/>
     <col min="9" max="9" width="17.140625" style="39" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="22.140625" style="39" customWidth="1"/>
-    <col min="11" max="11" width="28" style="39" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="28" style="39" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="61" t="s">
         <v>1002</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>588</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="72" t="s">
         <v>589</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="59" t="s">
         <v>590</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="59" t="s">
         <v>591</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="59" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4615,11 +4616,11 @@
       <c r="A3" s="39">
         <v>564179</v>
       </c>
-      <c r="B3" s="62">
+      <c r="B3" s="60">
         <v>45552</v>
       </c>
-      <c r="C3" s="57">
-        <v>45917</v>
+      <c r="C3" s="60">
+        <v>45552</v>
       </c>
       <c r="D3" s="39" t="s">
         <v>664</v>
@@ -4647,11 +4648,11 @@
       <c r="A4" s="39">
         <v>567880</v>
       </c>
-      <c r="B4" s="62">
+      <c r="B4" s="60">
         <v>45554</v>
       </c>
-      <c r="C4" s="57">
-        <v>45919</v>
+      <c r="C4" s="60">
+        <v>45554</v>
       </c>
       <c r="D4" s="39" t="s">
         <v>1005</v>
@@ -4676,11 +4677,11 @@
       <c r="A5" s="39">
         <v>471737</v>
       </c>
-      <c r="B5" s="62">
+      <c r="B5" s="60">
         <v>45553</v>
       </c>
-      <c r="C5" s="57">
-        <v>45917</v>
+      <c r="C5" s="60">
+        <v>45552</v>
       </c>
       <c r="D5" s="39" t="s">
         <v>1007</v>
@@ -4708,11 +4709,11 @@
       <c r="A6" s="39">
         <v>567226</v>
       </c>
-      <c r="B6" s="62">
+      <c r="B6" s="60">
         <v>45527</v>
       </c>
-      <c r="C6" s="57">
-        <v>45891</v>
+      <c r="C6" s="60">
+        <v>45526</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>717</v>
@@ -4737,11 +4738,11 @@
       <c r="A7" s="39">
         <v>564204</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="60">
         <v>45468</v>
       </c>
-      <c r="C7" s="57">
-        <v>45833</v>
+      <c r="C7" s="60">
+        <v>45468</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>744</v>
@@ -4761,7 +4762,7 @@
       <c r="K7" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="59" t="s">
+      <c r="L7" s="58" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -4769,11 +4770,11 @@
       <c r="A8" s="39">
         <v>564214</v>
       </c>
-      <c r="B8" s="62">
+      <c r="B8" s="60">
         <v>45525</v>
       </c>
-      <c r="C8" s="57">
-        <v>45889</v>
+      <c r="C8" s="60">
+        <v>45524</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>739</v>
@@ -4798,11 +4799,11 @@
       <c r="A9" s="39">
         <v>567067</v>
       </c>
-      <c r="B9" s="62">
+      <c r="B9" s="60">
         <v>45525</v>
       </c>
-      <c r="C9" s="57">
-        <v>45889</v>
+      <c r="C9" s="60">
+        <v>45524</v>
       </c>
       <c r="D9" s="39" t="s">
         <v>902</v>
@@ -4827,11 +4828,11 @@
       <c r="A10" s="39">
         <v>474896</v>
       </c>
-      <c r="B10" s="62">
+      <c r="B10" s="60">
         <v>45504</v>
       </c>
-      <c r="C10" s="57">
-        <v>45868</v>
+      <c r="C10" s="60">
+        <v>45503</v>
       </c>
       <c r="D10" s="39" t="s">
         <v>669</v>
@@ -4856,10 +4857,10 @@
       <c r="A11" s="39">
         <v>521924</v>
       </c>
-      <c r="B11" s="62">
+      <c r="B11" s="60">
         <v>45463</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D11" s="39" t="s">
@@ -4879,11 +4880,11 @@
       <c r="A12" s="39">
         <v>569507</v>
       </c>
-      <c r="B12" s="62">
+      <c r="B12" s="60">
         <v>45516</v>
       </c>
-      <c r="C12" s="57">
-        <v>45881</v>
+      <c r="C12" s="60">
+        <v>45516</v>
       </c>
       <c r="E12" s="39" t="s">
         <v>1022</v>
@@ -4900,7 +4901,7 @@
       <c r="K12" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="L12" s="59" t="s">
+      <c r="L12" s="58" t="s">
         <v>1023</v>
       </c>
     </row>
@@ -4908,13 +4909,13 @@
       <c r="A13" s="39">
         <v>564107</v>
       </c>
-      <c r="B13" s="62">
+      <c r="B13" s="60">
         <v>45510</v>
       </c>
-      <c r="C13" s="57">
-        <v>45875</v>
-      </c>
-      <c r="D13" s="58" t="s">
+      <c r="C13" s="60">
+        <v>45510</v>
+      </c>
+      <c r="D13" s="57" t="s">
         <v>947</v>
       </c>
       <c r="E13" s="39" t="s">
@@ -4932,7 +4933,7 @@
       <c r="K13" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="L13" s="59" t="s">
+      <c r="L13" s="58" t="s">
         <v>1025</v>
       </c>
     </row>
@@ -4940,11 +4941,11 @@
       <c r="A14" s="39">
         <v>471754</v>
       </c>
-      <c r="B14" s="62">
+      <c r="B14" s="60">
         <v>45538</v>
       </c>
-      <c r="C14" s="57">
-        <v>45903</v>
+      <c r="C14" s="60">
+        <v>45538</v>
       </c>
       <c r="D14" s="39" t="s">
         <v>1026</v>
@@ -4969,10 +4970,10 @@
       <c r="A15" s="39">
         <v>567265</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="60">
         <v>45562</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D15" s="39" t="s">
@@ -4998,10 +4999,10 @@
       <c r="A16" s="39">
         <v>564161</v>
       </c>
-      <c r="B16" s="62">
+      <c r="B16" s="60">
         <v>45531</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="60" t="s">
         <v>486</v>
       </c>
       <c r="D16" s="39" t="s">
@@ -5027,10 +5028,10 @@
       <c r="A17" s="39">
         <v>564066</v>
       </c>
-      <c r="B17" s="62">
+      <c r="B17" s="60">
         <v>45531</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D17" s="39" t="s">
@@ -5054,7 +5055,7 @@
       <c r="K17" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="L17" s="59" t="s">
+      <c r="L17" s="58" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -5062,10 +5063,10 @@
       <c r="A18" s="39">
         <v>564434</v>
       </c>
-      <c r="B18" s="62">
+      <c r="B18" s="60">
         <v>45533</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D18" s="39" t="s">
@@ -5091,10 +5092,10 @@
       <c r="A19" s="39">
         <v>577797</v>
       </c>
-      <c r="B19" s="62">
+      <c r="B19" s="60">
         <v>45533</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D19" s="39" t="s">
@@ -5120,10 +5121,10 @@
       <c r="A20" s="39">
         <v>578873</v>
       </c>
-      <c r="B20" s="62">
+      <c r="B20" s="60">
         <v>45534</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D20" s="39" t="s">
@@ -5149,10 +5150,10 @@
       <c r="A21" s="39">
         <v>564202</v>
       </c>
-      <c r="B21" s="62">
+      <c r="B21" s="60">
         <v>45534</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D21" s="39" t="s">
@@ -5178,10 +5179,10 @@
       <c r="A22" s="39">
         <v>564961</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="60">
         <v>45534</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="D22" s="39" t="s">
@@ -5207,11 +5208,11 @@
       <c r="A23" s="39">
         <v>577781</v>
       </c>
-      <c r="B23" s="62">
+      <c r="B23" s="60">
         <v>45561</v>
       </c>
-      <c r="C23" s="57">
-        <v>45926</v>
+      <c r="C23" s="60">
+        <v>45561</v>
       </c>
       <c r="D23" s="39" t="s">
         <v>818</v>
@@ -5231,7 +5232,7 @@
       <c r="K23" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="L23" s="59" t="s">
+      <c r="L23" s="58" t="s">
         <v>1041</v>
       </c>
     </row>
@@ -5239,11 +5240,11 @@
       <c r="A24" s="39">
         <v>567029</v>
       </c>
-      <c r="B24" s="62">
+      <c r="B24" s="60">
         <v>45561</v>
       </c>
-      <c r="C24" s="57">
-        <v>45924</v>
+      <c r="C24" s="60">
+        <v>45559</v>
       </c>
       <c r="D24" s="39" t="s">
         <v>838</v>
@@ -5263,7 +5264,7 @@
       <c r="K24" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="L24" s="59" t="s">
+      <c r="L24" s="58" t="s">
         <v>1041</v>
       </c>
     </row>
@@ -5271,13 +5272,13 @@
       <c r="A25" s="39">
         <v>575814</v>
       </c>
-      <c r="B25" s="62">
+      <c r="B25" s="60">
         <v>45301</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="60" t="s">
         <v>1046</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="57">
         <v>0.25347222222222221</v>
       </c>
       <c r="E25" s="39" t="s">
@@ -5297,10 +5298,10 @@
       <c r="A26" s="39">
         <v>569623</v>
       </c>
-      <c r="B26" s="62">
+      <c r="B26" s="60">
         <v>45300</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D26" s="39" t="s">
@@ -5323,10 +5324,10 @@
       <c r="A27" s="39">
         <v>567881</v>
       </c>
-      <c r="B27" s="62">
+      <c r="B27" s="60">
         <v>45583</v>
       </c>
-      <c r="C27" s="61">
+      <c r="C27" s="60">
         <v>45506</v>
       </c>
       <c r="D27" s="39" t="s">
@@ -5349,10 +5350,10 @@
       <c r="A28" s="39">
         <v>567083</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="60">
         <v>45439</v>
       </c>
-      <c r="C28" s="61">
+      <c r="C28" s="60">
         <v>45174</v>
       </c>
       <c r="D28" s="39" t="s">
@@ -5381,10 +5382,10 @@
       <c r="A29" s="39">
         <v>528137</v>
       </c>
-      <c r="B29" s="62">
+      <c r="B29" s="60">
         <v>45439</v>
       </c>
-      <c r="C29" s="61">
+      <c r="C29" s="60">
         <v>45176</v>
       </c>
       <c r="D29" s="39" t="s">
@@ -5413,10 +5414,10 @@
       <c r="A30" s="39">
         <v>567428</v>
       </c>
-      <c r="B30" s="62">
+      <c r="B30" s="60">
         <v>45439</v>
       </c>
-      <c r="C30" s="61">
+      <c r="C30" s="60">
         <v>45176</v>
       </c>
       <c r="D30" s="39" t="s">
@@ -5445,10 +5446,10 @@
       <c r="A31" s="39">
         <v>567482</v>
       </c>
-      <c r="B31" s="62">
+      <c r="B31" s="60">
         <v>45429</v>
       </c>
-      <c r="C31" s="61">
+      <c r="C31" s="60">
         <v>45170</v>
       </c>
       <c r="D31" s="39" t="s">
@@ -5483,10 +5484,10 @@
       <c r="A32" s="39">
         <v>569215</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="60">
         <v>45429</v>
       </c>
-      <c r="C32" s="61">
+      <c r="C32" s="60">
         <v>45170</v>
       </c>
       <c r="D32" s="39" t="s">
@@ -5521,10 +5522,10 @@
       <c r="A33" s="39">
         <v>569032</v>
       </c>
-      <c r="B33" s="62">
+      <c r="B33" s="60">
         <v>45429</v>
       </c>
-      <c r="C33" s="61">
+      <c r="C33" s="60">
         <v>45170</v>
       </c>
       <c r="D33" s="39" t="s">
@@ -5559,10 +5560,10 @@
       <c r="A34" s="39">
         <v>471466</v>
       </c>
-      <c r="B34" s="62">
+      <c r="B34" s="60">
         <v>45429</v>
       </c>
-      <c r="C34" s="61">
+      <c r="C34" s="60">
         <v>45167</v>
       </c>
       <c r="D34" s="39" t="s">
@@ -5600,10 +5601,10 @@
       <c r="A35" s="39">
         <v>564145</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="60">
         <v>45429</v>
       </c>
-      <c r="C35" s="61">
+      <c r="C35" s="60">
         <v>45167</v>
       </c>
       <c r="D35" s="39" t="s">
@@ -5641,10 +5642,10 @@
       <c r="A36" s="39">
         <v>564460</v>
       </c>
-      <c r="B36" s="62">
+      <c r="B36" s="60">
         <v>45428</v>
       </c>
-      <c r="C36" s="61">
+      <c r="C36" s="60">
         <v>45170</v>
       </c>
       <c r="D36" s="39" t="s">
@@ -5679,10 +5680,10 @@
       <c r="A37" s="39">
         <v>564341</v>
       </c>
-      <c r="B37" s="62">
+      <c r="B37" s="60">
         <v>45428</v>
       </c>
-      <c r="C37" s="61">
+      <c r="C37" s="60">
         <v>45170</v>
       </c>
       <c r="D37" s="39" t="s">
@@ -5717,10 +5718,10 @@
       <c r="A38" s="39">
         <v>564756</v>
       </c>
-      <c r="B38" s="62">
+      <c r="B38" s="60">
         <v>45438</v>
       </c>
-      <c r="C38" s="61">
+      <c r="C38" s="60">
         <v>45184</v>
       </c>
       <c r="D38" s="39" t="s">
@@ -5755,10 +5756,10 @@
       <c r="A39" s="39">
         <v>563807</v>
       </c>
-      <c r="B39" s="62">
+      <c r="B39" s="60">
         <v>45378</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="60" t="s">
         <v>1195</v>
       </c>
       <c r="D39" s="39" t="s">
@@ -5781,10 +5782,10 @@
       <c r="A40" s="39">
         <v>574694</v>
       </c>
-      <c r="B40" s="62">
+      <c r="B40" s="60">
         <v>45376</v>
       </c>
-      <c r="C40" s="61">
+      <c r="C40" s="60">
         <v>45184</v>
       </c>
       <c r="D40" s="39" t="s">
@@ -5819,10 +5820,10 @@
       <c r="A41" s="39">
         <v>577472</v>
       </c>
-      <c r="B41" s="62">
+      <c r="B41" s="60">
         <v>45375</v>
       </c>
-      <c r="C41" s="61">
+      <c r="C41" s="60">
         <v>45174</v>
       </c>
       <c r="D41" s="39" t="s">
@@ -5857,10 +5858,10 @@
       <c r="A42" s="39">
         <v>572457</v>
       </c>
-      <c r="B42" s="62">
+      <c r="B42" s="60">
         <v>45372</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="60" t="s">
         <v>1201</v>
       </c>
       <c r="D42" s="39" t="s">
@@ -5880,10 +5881,10 @@
       <c r="A43" s="39">
         <v>567442</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="60">
         <v>45370</v>
       </c>
-      <c r="C43" s="61">
+      <c r="C43" s="60">
         <v>45174</v>
       </c>
       <c r="D43" s="39" t="s">
@@ -5912,10 +5913,10 @@
       <c r="A44" s="39">
         <v>564416</v>
       </c>
-      <c r="B44" s="62">
+      <c r="B44" s="60">
         <v>45369</v>
       </c>
-      <c r="C44" s="61">
+      <c r="C44" s="60">
         <v>45174</v>
       </c>
       <c r="D44" s="39" t="s">
@@ -5944,10 +5945,10 @@
       <c r="A45" s="39">
         <v>567465</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="60">
         <v>45369</v>
       </c>
-      <c r="C45" s="61">
+      <c r="C45" s="60">
         <v>45174</v>
       </c>
       <c r="D45" s="39" t="s">
@@ -5976,13 +5977,13 @@
       <c r="A46" s="39">
         <v>564456</v>
       </c>
-      <c r="B46" s="62">
+      <c r="B46" s="60">
         <v>45369</v>
       </c>
-      <c r="C46" s="61">
+      <c r="C46" s="60">
         <v>45174</v>
       </c>
-      <c r="D46" s="58">
+      <c r="D46" s="57">
         <v>0.43402777777777779</v>
       </c>
       <c r="E46" s="39" t="s">
@@ -6008,10 +6009,10 @@
       <c r="A47" s="39">
         <v>564640</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="60">
         <v>45369</v>
       </c>
-      <c r="C47" s="61">
+      <c r="C47" s="60">
         <v>45174</v>
       </c>
       <c r="D47" s="39" t="s">
@@ -6040,10 +6041,10 @@
       <c r="A48" s="39">
         <v>567923</v>
       </c>
-      <c r="B48" s="62">
+      <c r="B48" s="60">
         <v>45369</v>
       </c>
-      <c r="C48" s="61">
+      <c r="C48" s="60">
         <v>45174</v>
       </c>
       <c r="D48" s="39" t="s">
@@ -6072,10 +6073,10 @@
       <c r="A49" s="39">
         <v>564713</v>
       </c>
-      <c r="B49" s="62">
+      <c r="B49" s="60">
         <v>45369</v>
       </c>
-      <c r="C49" s="61">
+      <c r="C49" s="60">
         <v>45168</v>
       </c>
       <c r="D49" s="39" t="s">
@@ -6110,10 +6111,10 @@
       <c r="A50" s="39">
         <v>564637</v>
       </c>
-      <c r="B50" s="62">
+      <c r="B50" s="60">
         <v>45371</v>
       </c>
-      <c r="C50" s="61">
+      <c r="C50" s="60">
         <v>45168</v>
       </c>
       <c r="D50" s="39" t="s">
@@ -6148,10 +6149,10 @@
       <c r="A51" s="39">
         <v>564334</v>
       </c>
-      <c r="B51" s="62">
+      <c r="B51" s="60">
         <v>45371</v>
       </c>
-      <c r="C51" s="61">
+      <c r="C51" s="60">
         <v>45168</v>
       </c>
       <c r="D51" s="39" t="s">
@@ -6186,10 +6187,10 @@
       <c r="A52" s="39">
         <v>564312</v>
       </c>
-      <c r="B52" s="62">
+      <c r="B52" s="60">
         <v>45371</v>
       </c>
-      <c r="C52" s="61">
+      <c r="C52" s="60">
         <v>45168</v>
       </c>
       <c r="D52" s="39" t="s">
@@ -6224,10 +6225,10 @@
       <c r="A53" s="39">
         <v>564349</v>
       </c>
-      <c r="B53" s="62">
+      <c r="B53" s="60">
         <v>45371</v>
       </c>
-      <c r="C53" s="61">
+      <c r="C53" s="60">
         <v>45174</v>
       </c>
       <c r="D53" s="39" t="s">
@@ -6256,10 +6257,10 @@
       <c r="A54" s="39">
         <v>564783</v>
       </c>
-      <c r="B54" s="62">
+      <c r="B54" s="60">
         <v>45366</v>
       </c>
-      <c r="C54" s="61">
+      <c r="C54" s="60">
         <v>45168</v>
       </c>
       <c r="D54" s="39" t="s">
@@ -6288,10 +6289,10 @@
       <c r="A55" s="39">
         <v>564604</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="60">
         <v>45366</v>
       </c>
-      <c r="C55" s="61">
+      <c r="C55" s="60">
         <v>45168</v>
       </c>
       <c r="D55" s="39" t="s">
@@ -6320,10 +6321,10 @@
       <c r="A56" s="39">
         <v>564864</v>
       </c>
-      <c r="B56" s="62">
+      <c r="B56" s="60">
         <v>45366</v>
       </c>
-      <c r="C56" s="61">
+      <c r="C56" s="60">
         <v>45168</v>
       </c>
       <c r="D56" s="39" t="s">
@@ -6352,10 +6353,10 @@
       <c r="A57" s="39">
         <v>564417</v>
       </c>
-      <c r="B57" s="62">
+      <c r="B57" s="60">
         <v>45366</v>
       </c>
-      <c r="C57" s="61">
+      <c r="C57" s="60">
         <v>45168</v>
       </c>
       <c r="D57" s="39" t="s">
@@ -6384,10 +6385,10 @@
       <c r="A58" s="39">
         <v>564590</v>
       </c>
-      <c r="B58" s="62">
+      <c r="B58" s="60">
         <v>45366</v>
       </c>
-      <c r="C58" s="39" t="s">
+      <c r="C58" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D58" s="39" t="s">
@@ -6407,10 +6408,10 @@
       <c r="A59" s="39">
         <v>564764</v>
       </c>
-      <c r="B59" s="62">
+      <c r="B59" s="60">
         <v>45366</v>
       </c>
-      <c r="C59" s="61">
+      <c r="C59" s="60">
         <v>45168</v>
       </c>
       <c r="D59" s="39" t="s">
@@ -6439,10 +6440,10 @@
       <c r="A60" s="39">
         <v>564554</v>
       </c>
-      <c r="B60" s="62">
+      <c r="B60" s="60">
         <v>45366</v>
       </c>
-      <c r="C60" s="61">
+      <c r="C60" s="60">
         <v>45168</v>
       </c>
       <c r="D60" s="39" t="s">
@@ -6471,10 +6472,10 @@
       <c r="A61" s="39">
         <v>564761</v>
       </c>
-      <c r="B61" s="62">
+      <c r="B61" s="60">
         <v>45366</v>
       </c>
-      <c r="C61" s="61">
+      <c r="C61" s="60">
         <v>45168</v>
       </c>
       <c r="D61" s="39" t="s">
@@ -6503,10 +6504,10 @@
       <c r="A62" s="39">
         <v>564463</v>
       </c>
-      <c r="B62" s="62">
+      <c r="B62" s="60">
         <v>45367</v>
       </c>
-      <c r="C62" s="61">
+      <c r="C62" s="60">
         <v>45168</v>
       </c>
       <c r="D62" s="39" t="s">
@@ -6535,10 +6536,10 @@
       <c r="A63" s="39">
         <v>473112</v>
       </c>
-      <c r="B63" s="62">
+      <c r="B63" s="60">
         <v>45367</v>
       </c>
-      <c r="C63" s="61">
+      <c r="C63" s="60">
         <v>45168</v>
       </c>
       <c r="D63" s="39" t="s">
@@ -6573,10 +6574,10 @@
       <c r="A64" s="39">
         <v>471616</v>
       </c>
-      <c r="B64" s="62">
+      <c r="B64" s="60">
         <v>45366</v>
       </c>
-      <c r="C64" s="61">
+      <c r="C64" s="60">
         <v>45168</v>
       </c>
       <c r="D64" s="39" t="s">
@@ -6611,10 +6612,10 @@
       <c r="A65" s="39">
         <v>564411</v>
       </c>
-      <c r="B65" s="62">
+      <c r="B65" s="60">
         <v>45367</v>
       </c>
-      <c r="C65" s="61">
+      <c r="C65" s="60">
         <v>45168</v>
       </c>
       <c r="D65" s="39" t="s">
@@ -6649,10 +6650,10 @@
       <c r="A66" s="39">
         <v>564358</v>
       </c>
-      <c r="B66" s="62">
+      <c r="B66" s="60">
         <v>45367</v>
       </c>
-      <c r="C66" s="61">
+      <c r="C66" s="60">
         <v>45168</v>
       </c>
       <c r="D66" s="39" t="s">
@@ -6687,10 +6688,10 @@
       <c r="A67" s="39">
         <v>532075</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="60">
         <v>45366</v>
       </c>
-      <c r="C67" s="61">
+      <c r="C67" s="60">
         <v>45168</v>
       </c>
       <c r="D67" s="39" t="s">
@@ -6725,10 +6726,10 @@
       <c r="A68" s="39">
         <v>471558</v>
       </c>
-      <c r="B68" s="62">
+      <c r="B68" s="60">
         <v>45367</v>
       </c>
-      <c r="C68" s="61">
+      <c r="C68" s="60">
         <v>45168</v>
       </c>
       <c r="D68" s="39" t="s">
@@ -6763,10 +6764,10 @@
       <c r="A69" s="39">
         <v>574362</v>
       </c>
-      <c r="B69" s="62">
+      <c r="B69" s="60">
         <v>45353</v>
       </c>
-      <c r="C69" s="61">
+      <c r="C69" s="60">
         <v>45190</v>
       </c>
       <c r="D69" s="39" t="s">
@@ -6801,10 +6802,10 @@
       <c r="A70" s="39">
         <v>528324</v>
       </c>
-      <c r="B70" s="62">
+      <c r="B70" s="60">
         <v>45356</v>
       </c>
-      <c r="C70" s="61">
+      <c r="C70" s="60">
         <v>45188</v>
       </c>
       <c r="D70" s="39" t="s">
@@ -6833,10 +6834,10 @@
       <c r="A71" s="39">
         <v>532292</v>
       </c>
-      <c r="B71" s="62">
+      <c r="B71" s="60">
         <v>45350</v>
       </c>
-      <c r="C71" s="61">
+      <c r="C71" s="60">
         <v>45187</v>
       </c>
       <c r="D71" s="39" t="s">
@@ -6865,10 +6866,10 @@
       <c r="A72" s="39">
         <v>528811</v>
       </c>
-      <c r="B72" s="62">
+      <c r="B72" s="60">
         <v>45342</v>
       </c>
-      <c r="C72" s="61">
+      <c r="C72" s="60">
         <v>45182</v>
       </c>
       <c r="D72" s="39" t="s">
@@ -6903,10 +6904,10 @@
       <c r="A73" s="39">
         <v>533396</v>
       </c>
-      <c r="B73" s="62">
+      <c r="B73" s="60">
         <v>45323</v>
       </c>
-      <c r="C73" s="61">
+      <c r="C73" s="60">
         <v>45195</v>
       </c>
       <c r="D73" s="39" t="s">
@@ -6941,10 +6942,10 @@
       <c r="A74" s="39">
         <v>567493</v>
       </c>
-      <c r="B74" s="62">
+      <c r="B74" s="60">
         <v>45324</v>
       </c>
-      <c r="C74" s="61">
+      <c r="C74" s="60">
         <v>45184</v>
       </c>
       <c r="D74" s="39" t="s">
@@ -6979,10 +6980,10 @@
       <c r="A75" s="39">
         <v>564857</v>
       </c>
-      <c r="B75" s="62">
+      <c r="B75" s="60">
         <v>45302</v>
       </c>
-      <c r="C75" s="39" t="s">
+      <c r="C75" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D75" s="39" t="s">
@@ -7002,10 +7003,10 @@
       <c r="A76" s="39">
         <v>567627</v>
       </c>
-      <c r="B76" s="62">
+      <c r="B76" s="60">
         <v>45302</v>
       </c>
-      <c r="C76" s="39" t="s">
+      <c r="C76" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D76" s="39" t="s">
@@ -7025,10 +7026,10 @@
       <c r="A77" s="39">
         <v>564566</v>
       </c>
-      <c r="B77" s="62">
+      <c r="B77" s="60">
         <v>45302</v>
       </c>
-      <c r="C77" s="39" t="s">
+      <c r="C77" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D77" s="39" t="s">
@@ -7048,10 +7049,10 @@
       <c r="A78" s="39">
         <v>564942</v>
       </c>
-      <c r="B78" s="62">
+      <c r="B78" s="60">
         <v>45302</v>
       </c>
-      <c r="C78" s="39" t="s">
+      <c r="C78" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D78" s="39" t="s">
@@ -7071,10 +7072,10 @@
       <c r="A79" s="39">
         <v>564662</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="60">
         <v>45302</v>
       </c>
-      <c r="C79" s="39" t="s">
+      <c r="C79" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D79" s="39" t="s">
@@ -7094,10 +7095,10 @@
       <c r="A80" s="39">
         <v>564401</v>
       </c>
-      <c r="B80" s="62">
+      <c r="B80" s="60">
         <v>45302</v>
       </c>
-      <c r="C80" s="39" t="s">
+      <c r="C80" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D80" s="39" t="s">
@@ -7117,10 +7118,10 @@
       <c r="A81" s="39">
         <v>572411</v>
       </c>
-      <c r="B81" s="62">
+      <c r="B81" s="60">
         <v>45302</v>
       </c>
-      <c r="C81" s="61">
+      <c r="C81" s="60">
         <v>45078</v>
       </c>
       <c r="D81" s="39" t="s">
@@ -7140,10 +7141,10 @@
       <c r="A82" s="39">
         <v>563884</v>
       </c>
-      <c r="B82" s="62">
+      <c r="B82" s="60">
         <v>45302</v>
       </c>
-      <c r="C82" s="39" t="s">
+      <c r="C82" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D82" s="39" t="s">
@@ -7163,10 +7164,10 @@
       <c r="A83" s="39">
         <v>564322</v>
       </c>
-      <c r="B83" s="62">
+      <c r="B83" s="60">
         <v>45303</v>
       </c>
-      <c r="C83" s="39" t="s">
+      <c r="C83" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D83" s="39" t="s">
@@ -7186,10 +7187,10 @@
       <c r="A84" s="39">
         <v>471403</v>
       </c>
-      <c r="B84" s="62">
+      <c r="B84" s="60">
         <v>45303</v>
       </c>
-      <c r="C84" s="39" t="s">
+      <c r="C84" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D84" s="39" t="s">
@@ -7209,10 +7210,10 @@
       <c r="A85" s="39">
         <v>564333</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="60">
         <v>45303</v>
       </c>
-      <c r="C85" s="39" t="s">
+      <c r="C85" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D85" s="39" t="s">
@@ -7232,13 +7233,13 @@
       <c r="A86" s="39">
         <v>572490</v>
       </c>
-      <c r="B86" s="62">
+      <c r="B86" s="60">
         <v>45303</v>
       </c>
-      <c r="C86" s="39" t="s">
+      <c r="C86" s="60" t="s">
         <v>1046</v>
       </c>
-      <c r="D86" s="58">
+      <c r="D86" s="57">
         <v>0.41666666666666669</v>
       </c>
       <c r="E86" s="39" t="s">
@@ -7255,13 +7256,13 @@
       <c r="A87" s="39">
         <v>564476</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="60">
         <v>45303</v>
       </c>
-      <c r="C87" s="39" t="s">
+      <c r="C87" s="60" t="s">
         <v>1046</v>
       </c>
-      <c r="D87" s="58">
+      <c r="D87" s="57">
         <v>0.4201388888888889</v>
       </c>
       <c r="E87" s="39" t="s">
@@ -7278,10 +7279,10 @@
       <c r="A88" s="39">
         <v>563708</v>
       </c>
-      <c r="B88" s="62">
+      <c r="B88" s="60">
         <v>45303</v>
       </c>
-      <c r="C88" s="39" t="s">
+      <c r="C88" s="60" t="s">
         <v>1046</v>
       </c>
       <c r="D88" s="39" t="s">
@@ -7301,10 +7302,10 @@
       <c r="A89" s="39">
         <v>572482</v>
       </c>
-      <c r="B89" s="62">
+      <c r="B89" s="60">
         <v>45295</v>
       </c>
-      <c r="C89" s="61">
+      <c r="C89" s="60">
         <v>45167</v>
       </c>
       <c r="D89" s="39" t="s">
@@ -7324,10 +7325,10 @@
       <c r="A90" s="39">
         <v>471259</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="60">
         <v>45295</v>
       </c>
-      <c r="C90" s="61">
+      <c r="C90" s="60">
         <v>45167</v>
       </c>
       <c r="D90" s="39" t="s">
@@ -7347,13 +7348,13 @@
       <c r="A91" s="39">
         <v>567570</v>
       </c>
-      <c r="B91" s="62">
+      <c r="B91" s="60">
         <v>45294</v>
       </c>
-      <c r="C91" s="61">
+      <c r="C91" s="60">
         <v>45175</v>
       </c>
-      <c r="D91" s="58">
+      <c r="D91" s="57">
         <v>0.3923611111111111</v>
       </c>
       <c r="E91" s="39" t="s">
@@ -7370,10 +7371,10 @@
       <c r="A92" s="39">
         <v>522966</v>
       </c>
-      <c r="B92" s="62">
+      <c r="B92" s="60">
         <v>45272</v>
       </c>
-      <c r="C92" s="61">
+      <c r="C92" s="60">
         <v>44823</v>
       </c>
       <c r="D92" s="39" t="s">
@@ -7393,10 +7394,10 @@
       <c r="A93" s="39">
         <v>500534</v>
       </c>
-      <c r="B93" s="62">
+      <c r="B93" s="60">
         <v>45272</v>
       </c>
-      <c r="C93" s="61">
+      <c r="C93" s="60">
         <v>45184</v>
       </c>
       <c r="D93" s="39" t="s">
@@ -7416,10 +7417,10 @@
       <c r="A94" s="39">
         <v>563741</v>
       </c>
-      <c r="B94" s="62">
+      <c r="B94" s="60">
         <v>45272</v>
       </c>
-      <c r="C94" s="61">
+      <c r="C94" s="60">
         <v>45161</v>
       </c>
       <c r="D94" s="39" t="s">
@@ -7439,13 +7440,13 @@
       <c r="A95" s="39">
         <v>564354</v>
       </c>
-      <c r="B95" s="62">
+      <c r="B95" s="60">
         <v>45272</v>
       </c>
-      <c r="C95" s="61">
+      <c r="C95" s="60">
         <v>45176</v>
       </c>
-      <c r="D95" s="58">
+      <c r="D95" s="57">
         <v>0.39930555555555558</v>
       </c>
       <c r="E95" s="39" t="s">
@@ -7462,10 +7463,10 @@
       <c r="A96" s="39">
         <v>603928</v>
       </c>
-      <c r="B96" s="62">
+      <c r="B96" s="60">
         <v>45272</v>
       </c>
-      <c r="C96" s="61">
+      <c r="C96" s="60">
         <v>44803</v>
       </c>
       <c r="D96" s="39" t="s">
@@ -7485,13 +7486,13 @@
       <c r="A97" s="39">
         <v>502414</v>
       </c>
-      <c r="B97" s="62">
+      <c r="B97" s="60">
         <v>45272</v>
       </c>
-      <c r="C97" s="61">
+      <c r="C97" s="60">
         <v>44823</v>
       </c>
-      <c r="D97" s="58">
+      <c r="D97" s="57">
         <v>0.44791666666666669</v>
       </c>
       <c r="E97" s="39" t="s">
@@ -7508,13 +7509,13 @@
       <c r="A98" s="39">
         <v>471581</v>
       </c>
-      <c r="B98" s="62">
+      <c r="B98" s="60">
         <v>45247</v>
       </c>
-      <c r="C98" s="61">
+      <c r="C98" s="60">
         <v>45177</v>
       </c>
-      <c r="D98" s="58">
+      <c r="D98" s="57">
         <v>0.44791666666666669</v>
       </c>
       <c r="E98" s="39" t="s">
@@ -7531,10 +7532,10 @@
       <c r="A99" s="39">
         <v>567510</v>
       </c>
-      <c r="B99" s="62">
+      <c r="B99" s="60">
         <v>45247</v>
       </c>
-      <c r="C99" s="61">
+      <c r="C99" s="60">
         <v>45176</v>
       </c>
       <c r="D99" s="39" t="s">
@@ -7554,10 +7555,10 @@
       <c r="A100" s="39">
         <v>564891</v>
       </c>
-      <c r="B100" s="62">
+      <c r="B100" s="60">
         <v>45247</v>
       </c>
-      <c r="C100" s="61">
+      <c r="C100" s="60">
         <v>45176</v>
       </c>
       <c r="D100" s="39" t="s">
@@ -7577,10 +7578,10 @@
       <c r="A101" s="39">
         <v>471841</v>
       </c>
-      <c r="B101" s="62">
+      <c r="B101" s="60">
         <v>45247</v>
       </c>
-      <c r="C101" s="61">
+      <c r="C101" s="60">
         <v>45176</v>
       </c>
       <c r="D101" s="39" t="s">
@@ -7600,13 +7601,13 @@
       <c r="A102" s="39">
         <v>567176</v>
       </c>
-      <c r="B102" s="62">
+      <c r="B102" s="60">
         <v>45250</v>
       </c>
-      <c r="C102" s="61">
+      <c r="C102" s="60">
         <v>45176</v>
       </c>
-      <c r="D102" s="58" t="s">
+      <c r="D102" s="57" t="s">
         <v>1137</v>
       </c>
       <c r="E102" s="39" t="s">
@@ -7623,10 +7624,10 @@
       <c r="A103" s="39">
         <v>502446</v>
       </c>
-      <c r="B103" s="62">
+      <c r="B103" s="60">
         <v>45250</v>
       </c>
-      <c r="C103" s="61">
+      <c r="C103" s="60">
         <v>45176</v>
       </c>
       <c r="D103" s="39" t="s">
@@ -7646,10 +7647,10 @@
       <c r="A104" s="39">
         <v>563703</v>
       </c>
-      <c r="B104" s="62">
+      <c r="B104" s="60">
         <v>45251</v>
       </c>
-      <c r="C104" s="61">
+      <c r="C104" s="60">
         <v>44803</v>
       </c>
       <c r="D104" s="39" t="s">
@@ -7669,10 +7670,10 @@
       <c r="A105" s="39">
         <v>564573</v>
       </c>
-      <c r="B105" s="62">
+      <c r="B105" s="60">
         <v>45251</v>
       </c>
-      <c r="C105" s="61">
+      <c r="C105" s="60">
         <v>44803</v>
       </c>
       <c r="D105" s="39" t="s">
@@ -7692,10 +7693,10 @@
       <c r="A106" s="39">
         <v>564038</v>
       </c>
-      <c r="B106" s="62">
+      <c r="B106" s="60">
         <v>45251</v>
       </c>
-      <c r="C106" s="61">
+      <c r="C106" s="60">
         <v>44803</v>
       </c>
       <c r="D106" s="39" t="s">
@@ -7715,10 +7716,10 @@
       <c r="A107" s="39">
         <v>564593</v>
       </c>
-      <c r="B107" s="62">
+      <c r="B107" s="60">
         <v>45251</v>
       </c>
-      <c r="C107" s="61">
+      <c r="C107" s="60">
         <v>44803</v>
       </c>
       <c r="D107" s="39" t="s">
@@ -7738,10 +7739,10 @@
       <c r="A108" s="39">
         <v>567439</v>
       </c>
-      <c r="B108" s="62">
+      <c r="B108" s="60">
         <v>45252</v>
       </c>
-      <c r="C108" s="61">
+      <c r="C108" s="60">
         <v>45161</v>
       </c>
       <c r="D108" s="39" t="s">
@@ -7761,10 +7762,10 @@
       <c r="A109" s="39">
         <v>577864</v>
       </c>
-      <c r="B109" s="62">
+      <c r="B109" s="60">
         <v>45253</v>
       </c>
-      <c r="C109" s="61">
+      <c r="C109" s="60">
         <v>45161</v>
       </c>
       <c r="D109" s="39" t="s">
@@ -7784,10 +7785,10 @@
       <c r="A110" s="39">
         <v>498720</v>
       </c>
-      <c r="B110" s="62">
+      <c r="B110" s="60">
         <v>45253</v>
       </c>
-      <c r="C110" s="61">
+      <c r="C110" s="60">
         <v>45161</v>
       </c>
       <c r="D110" s="39" t="s">
@@ -7807,10 +7808,10 @@
       <c r="A111" s="39">
         <v>563721</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="60">
         <v>45253</v>
       </c>
-      <c r="C111" s="61">
+      <c r="C111" s="60">
         <v>45161</v>
       </c>
       <c r="D111" s="39" t="s">
@@ -7830,10 +7831,10 @@
       <c r="A112" s="39">
         <v>603551</v>
       </c>
-      <c r="B112" s="62">
+      <c r="B112" s="60">
         <v>45257</v>
       </c>
-      <c r="C112" s="61">
+      <c r="C112" s="60">
         <v>45166</v>
       </c>
       <c r="D112" s="39" t="s">
@@ -7853,10 +7854,10 @@
       <c r="A113" s="39">
         <v>572673</v>
       </c>
-      <c r="B113" s="62">
+      <c r="B113" s="60">
         <v>45258</v>
       </c>
-      <c r="C113" s="61">
+      <c r="C113" s="60">
         <v>45166</v>
       </c>
       <c r="D113" s="39" t="s">
@@ -7876,13 +7877,13 @@
       <c r="A114" s="39">
         <v>471495</v>
       </c>
-      <c r="B114" s="62">
+      <c r="B114" s="60">
         <v>45250</v>
       </c>
-      <c r="C114" s="61">
+      <c r="C114" s="60">
         <v>45176</v>
       </c>
-      <c r="D114" s="58" t="s">
+      <c r="D114" s="57" t="s">
         <v>608</v>
       </c>
       <c r="E114" s="39" t="s">
@@ -7899,10 +7900,10 @@
       <c r="A115" s="39">
         <v>563788</v>
       </c>
-      <c r="B115" s="62">
+      <c r="B115" s="60">
         <v>45250</v>
       </c>
-      <c r="C115" s="61">
+      <c r="C115" s="60">
         <v>45176</v>
       </c>
       <c r="D115" s="39" t="s">
@@ -7922,10 +7923,10 @@
       <c r="A116" s="39">
         <v>563824</v>
       </c>
-      <c r="B116" s="62">
+      <c r="B116" s="60">
         <v>45250</v>
       </c>
-      <c r="C116" s="61">
+      <c r="C116" s="60">
         <v>45176</v>
       </c>
       <c r="D116" s="39" t="s">
@@ -7945,10 +7946,10 @@
       <c r="A117" s="39">
         <v>564740</v>
       </c>
-      <c r="B117" s="62">
+      <c r="B117" s="60">
         <v>45250</v>
       </c>
-      <c r="C117" s="61">
+      <c r="C117" s="60">
         <v>45188</v>
       </c>
       <c r="D117" s="39" t="s">
@@ -7968,10 +7969,10 @@
       <c r="A118" s="39">
         <v>567199</v>
       </c>
-      <c r="B118" s="62">
+      <c r="B118" s="60">
         <v>45250</v>
       </c>
-      <c r="C118" s="61">
+      <c r="C118" s="60">
         <v>45176</v>
       </c>
       <c r="D118" s="39" t="s">
@@ -7991,10 +7992,10 @@
       <c r="A119" s="39">
         <v>567221</v>
       </c>
-      <c r="B119" s="62">
+      <c r="B119" s="60">
         <v>45250</v>
       </c>
-      <c r="C119" s="61">
+      <c r="C119" s="60">
         <v>45176</v>
       </c>
       <c r="D119" s="39" t="s">
@@ -8014,10 +8015,10 @@
       <c r="A120" s="39">
         <v>564937</v>
       </c>
-      <c r="B120" s="62">
+      <c r="B120" s="60">
         <v>45250</v>
       </c>
-      <c r="C120" s="61">
+      <c r="C120" s="60">
         <v>45176</v>
       </c>
       <c r="D120" s="39" t="s">
@@ -8037,10 +8038,10 @@
       <c r="A121" s="39">
         <v>567116</v>
       </c>
-      <c r="B121" s="62">
+      <c r="B121" s="60">
         <v>45247</v>
       </c>
-      <c r="C121" s="61">
+      <c r="C121" s="60">
         <v>45177</v>
       </c>
       <c r="D121" s="39" t="s">
@@ -8060,10 +8061,10 @@
       <c r="A122" s="39">
         <v>471749</v>
       </c>
-      <c r="B122" s="62">
+      <c r="B122" s="60">
         <v>45247</v>
       </c>
-      <c r="C122" s="61">
+      <c r="C122" s="60">
         <v>45177</v>
       </c>
       <c r="D122" s="39" t="s">
@@ -8083,10 +8084,10 @@
       <c r="A123" s="39">
         <v>564842</v>
       </c>
-      <c r="B123" s="62">
+      <c r="B123" s="60">
         <v>45247</v>
       </c>
-      <c r="C123" s="61">
+      <c r="C123" s="60">
         <v>45177</v>
       </c>
       <c r="D123" s="39" t="s">
@@ -8106,10 +8107,10 @@
       <c r="A124" s="39">
         <v>567037</v>
       </c>
-      <c r="B124" s="62">
+      <c r="B124" s="60">
         <v>45247</v>
       </c>
-      <c r="C124" s="61">
+      <c r="C124" s="60">
         <v>45177</v>
       </c>
       <c r="D124" s="39" t="s">
@@ -8129,10 +8130,10 @@
       <c r="A125" s="39">
         <v>567200</v>
       </c>
-      <c r="B125" s="62">
+      <c r="B125" s="60">
         <v>45247</v>
       </c>
-      <c r="C125" s="61">
+      <c r="C125" s="60">
         <v>45176</v>
       </c>
       <c r="D125" s="39" t="s">
@@ -8152,10 +8153,10 @@
       <c r="A126" s="39">
         <v>564361</v>
       </c>
-      <c r="B126" s="62">
+      <c r="B126" s="60">
         <v>45247</v>
       </c>
-      <c r="C126" s="61">
+      <c r="C126" s="60">
         <v>45177</v>
       </c>
       <c r="D126" s="39" t="s">
@@ -8175,10 +8176,10 @@
       <c r="A127" s="39">
         <v>603692</v>
       </c>
-      <c r="B127" s="62">
+      <c r="B127" s="60">
         <v>45251</v>
       </c>
-      <c r="C127" s="61">
+      <c r="C127" s="60">
         <v>44804</v>
       </c>
       <c r="D127" s="39" t="s">
@@ -8198,10 +8199,10 @@
       <c r="A128" s="39">
         <v>578866</v>
       </c>
-      <c r="B128" s="62">
+      <c r="B128" s="60">
         <v>45252</v>
       </c>
-      <c r="C128" s="61">
+      <c r="C128" s="60">
         <v>45180</v>
       </c>
       <c r="D128" s="39" t="s">
@@ -8221,10 +8222,10 @@
       <c r="A129" s="39">
         <v>532142</v>
       </c>
-      <c r="B129" s="62">
+      <c r="B129" s="60">
         <v>45252</v>
       </c>
-      <c r="C129" s="61">
+      <c r="C129" s="60">
         <v>45176</v>
       </c>
       <c r="D129" s="39" t="s">
@@ -8244,10 +8245,10 @@
       <c r="A130" s="39">
         <v>578578</v>
       </c>
-      <c r="B130" s="62">
+      <c r="B130" s="60">
         <v>45252</v>
       </c>
-      <c r="C130" s="61">
+      <c r="C130" s="60">
         <v>45194</v>
       </c>
       <c r="D130" s="39" t="s">
@@ -8267,10 +8268,10 @@
       <c r="A131" s="39">
         <v>567565</v>
       </c>
-      <c r="B131" s="62">
+      <c r="B131" s="60">
         <v>45252</v>
       </c>
-      <c r="C131" s="61">
+      <c r="C131" s="60">
         <v>45194</v>
       </c>
       <c r="D131" s="39" t="s">
@@ -8290,13 +8291,13 @@
       <c r="A132" s="39">
         <v>532013</v>
       </c>
-      <c r="B132" s="62">
+      <c r="B132" s="60">
         <v>45252</v>
       </c>
-      <c r="C132" s="61">
+      <c r="C132" s="60">
         <v>45197</v>
       </c>
-      <c r="D132" s="58" t="s">
+      <c r="D132" s="57" t="s">
         <v>1121</v>
       </c>
       <c r="E132" s="39" t="s">
@@ -8313,10 +8314,10 @@
       <c r="A133" s="39">
         <v>564665</v>
       </c>
-      <c r="B133" s="62">
+      <c r="B133" s="60">
         <v>45247</v>
       </c>
-      <c r="C133" s="61">
+      <c r="C133" s="60">
         <v>45176</v>
       </c>
       <c r="D133" s="39" t="s">
@@ -8336,10 +8337,10 @@
       <c r="A134" s="39">
         <v>569218</v>
       </c>
-      <c r="B134" s="62">
+      <c r="B134" s="60">
         <v>45247</v>
       </c>
-      <c r="C134" s="61">
+      <c r="C134" s="60">
         <v>45167</v>
       </c>
       <c r="D134" s="39" t="s">
@@ -8359,10 +8360,10 @@
       <c r="A135" s="39">
         <v>564318</v>
       </c>
-      <c r="B135" s="62">
+      <c r="B135" s="60">
         <v>45250</v>
       </c>
-      <c r="C135" s="61">
+      <c r="C135" s="60">
         <v>45177</v>
       </c>
       <c r="D135" s="39" t="s">
@@ -8382,10 +8383,10 @@
       <c r="A136" s="39">
         <v>564016</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="60">
         <v>45247</v>
       </c>
-      <c r="C136" s="61">
+      <c r="C136" s="60">
         <v>45167</v>
       </c>
       <c r="D136" s="39" t="s">
@@ -8405,10 +8406,10 @@
       <c r="A137" s="39">
         <v>528653</v>
       </c>
-      <c r="B137" s="62">
+      <c r="B137" s="60">
         <v>45232</v>
       </c>
-      <c r="C137" s="61">
+      <c r="C137" s="60">
         <v>45167</v>
       </c>
       <c r="D137" s="39" t="s">
@@ -8428,10 +8429,10 @@
       <c r="A138" s="39">
         <v>567207</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="60">
         <v>45247</v>
       </c>
-      <c r="C138" s="61">
+      <c r="C138" s="60">
         <v>45175</v>
       </c>
       <c r="D138" s="39" t="s">
@@ -8457,10 +8458,10 @@
       <c r="A139" s="39">
         <v>563828</v>
       </c>
-      <c r="B139" s="62">
+      <c r="B139" s="60">
         <v>45244</v>
       </c>
-      <c r="C139" s="61">
+      <c r="C139" s="60">
         <v>45161</v>
       </c>
       <c r="D139" s="39" t="s">
@@ -8480,10 +8481,10 @@
       <c r="A140" s="39">
         <v>563764</v>
       </c>
-      <c r="B140" s="62">
+      <c r="B140" s="60">
         <v>45243</v>
       </c>
-      <c r="C140" s="61">
+      <c r="C140" s="60">
         <v>45161</v>
       </c>
       <c r="D140" s="39" t="s">
@@ -8503,10 +8504,10 @@
       <c r="A141" s="39">
         <v>532087</v>
       </c>
-      <c r="B141" s="62">
+      <c r="B141" s="60">
         <v>45237</v>
       </c>
-      <c r="C141" s="61">
+      <c r="C141" s="60">
         <v>45188</v>
       </c>
       <c r="D141" s="39" t="s">
@@ -8526,10 +8527,10 @@
       <c r="A142" s="39">
         <v>528707</v>
       </c>
-      <c r="B142" s="62">
+      <c r="B142" s="60">
         <v>45232</v>
       </c>
-      <c r="C142" s="61">
+      <c r="C142" s="60">
         <v>45167</v>
       </c>
       <c r="D142" s="39" t="s">
@@ -8549,10 +8550,10 @@
       <c r="A143" s="39">
         <v>500940</v>
       </c>
-      <c r="B143" s="62">
+      <c r="B143" s="60">
         <v>45246</v>
       </c>
-      <c r="C143" s="61">
+      <c r="C143" s="60">
         <v>45175</v>
       </c>
       <c r="D143" s="39" t="s">
@@ -8575,10 +8576,10 @@
       <c r="A144" s="39">
         <v>564319</v>
       </c>
-      <c r="B144" s="62">
+      <c r="B144" s="60">
         <v>45246</v>
       </c>
-      <c r="C144" s="61">
+      <c r="C144" s="60">
         <v>45176</v>
       </c>
       <c r="D144" s="39" t="s">
@@ -8601,10 +8602,10 @@
       <c r="A145" s="39">
         <v>563731</v>
       </c>
-      <c r="B145" s="62">
+      <c r="B145" s="60">
         <v>45243</v>
       </c>
-      <c r="C145" s="61">
+      <c r="C145" s="60">
         <v>45161</v>
       </c>
       <c r="D145" s="39" t="s">
@@ -8624,10 +8625,10 @@
       <c r="A146" s="39">
         <v>563727</v>
       </c>
-      <c r="B146" s="62">
+      <c r="B146" s="60">
         <v>45245</v>
       </c>
-      <c r="C146" s="61">
+      <c r="C146" s="60">
         <v>45161</v>
       </c>
       <c r="D146" s="39" t="s">
@@ -8647,10 +8648,10 @@
       <c r="A147" s="39">
         <v>563712</v>
       </c>
-      <c r="B147" s="62">
+      <c r="B147" s="60">
         <v>45243</v>
       </c>
-      <c r="C147" s="61">
+      <c r="C147" s="60">
         <v>45161</v>
       </c>
       <c r="D147" s="39" t="s">
@@ -8670,10 +8671,10 @@
       <c r="A148" s="39">
         <v>563757</v>
       </c>
-      <c r="B148" s="62">
+      <c r="B148" s="60">
         <v>45243</v>
       </c>
-      <c r="C148" s="61">
+      <c r="C148" s="60">
         <v>45161</v>
       </c>
       <c r="D148" s="39" t="s">
@@ -8693,10 +8694,10 @@
       <c r="A149" s="39">
         <v>563702</v>
       </c>
-      <c r="B149" s="62">
+      <c r="B149" s="60">
         <v>45243</v>
       </c>
-      <c r="C149" s="61">
+      <c r="C149" s="60">
         <v>45161</v>
       </c>
       <c r="D149" s="39" t="s">
@@ -8716,10 +8717,10 @@
       <c r="A150" s="39">
         <v>578675</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="60">
         <v>45243</v>
       </c>
-      <c r="C150" s="61">
+      <c r="C150" s="60">
         <v>45161</v>
       </c>
       <c r="D150" s="39" t="s">
@@ -8739,10 +8740,10 @@
       <c r="A151" s="39">
         <v>471823</v>
       </c>
-      <c r="B151" s="62">
+      <c r="B151" s="60">
         <v>45247</v>
       </c>
-      <c r="C151" s="61">
+      <c r="C151" s="60">
         <v>45175</v>
       </c>
       <c r="D151" s="39" t="s">
@@ -8765,10 +8766,10 @@
       <c r="A152" s="39">
         <v>577946</v>
       </c>
-      <c r="B152" s="62">
+      <c r="B152" s="60">
         <v>45239</v>
       </c>
-      <c r="C152" s="61">
+      <c r="C152" s="60">
         <v>45184</v>
       </c>
       <c r="D152" s="39" t="s">
@@ -8788,10 +8789,10 @@
       <c r="A153" s="39">
         <v>514040</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="60">
         <v>45239</v>
       </c>
-      <c r="C153" s="61">
+      <c r="C153" s="60">
         <v>45184</v>
       </c>
       <c r="D153" s="39" t="s">
@@ -8811,10 +8812,10 @@
       <c r="A154" s="39">
         <v>577445</v>
       </c>
-      <c r="B154" s="62">
+      <c r="B154" s="60">
         <v>45239</v>
       </c>
-      <c r="C154" s="61">
+      <c r="C154" s="60">
         <v>45184</v>
       </c>
       <c r="D154" s="39" t="s">
@@ -8834,10 +8835,10 @@
       <c r="A155" s="39">
         <v>569057</v>
       </c>
-      <c r="B155" s="62">
+      <c r="B155" s="60">
         <v>45238</v>
       </c>
-      <c r="C155" s="61">
+      <c r="C155" s="60">
         <v>45184</v>
       </c>
       <c r="D155" s="39" t="s">
@@ -8857,10 +8858,10 @@
       <c r="A156" s="39">
         <v>594136</v>
       </c>
-      <c r="B156" s="62">
+      <c r="B156" s="60">
         <v>45238</v>
       </c>
-      <c r="C156" s="61">
+      <c r="C156" s="60">
         <v>45176</v>
       </c>
       <c r="D156" s="39" t="s">
@@ -8883,10 +8884,10 @@
       <c r="A157" s="39">
         <v>569147</v>
       </c>
-      <c r="B157" s="62">
+      <c r="B157" s="60">
         <v>45238</v>
       </c>
-      <c r="C157" s="61">
+      <c r="C157" s="60">
         <v>45184</v>
       </c>
       <c r="D157" s="39" t="s">
@@ -8906,10 +8907,10 @@
       <c r="A158" s="39">
         <v>564852</v>
       </c>
-      <c r="B158" s="62">
+      <c r="B158" s="60">
         <v>45238</v>
       </c>
-      <c r="C158" s="61">
+      <c r="C158" s="60">
         <v>45176</v>
       </c>
       <c r="D158" s="39" t="s">
@@ -8932,10 +8933,10 @@
       <c r="A159" s="39">
         <v>567157</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="60">
         <v>45238</v>
       </c>
-      <c r="C159" s="61">
+      <c r="C159" s="60">
         <v>45184</v>
       </c>
       <c r="D159" s="39" t="s">
@@ -8955,10 +8956,10 @@
       <c r="A160" s="39">
         <v>567224</v>
       </c>
-      <c r="B160" s="62">
+      <c r="B160" s="60">
         <v>45238</v>
       </c>
-      <c r="C160" s="61">
+      <c r="C160" s="60">
         <v>45176</v>
       </c>
       <c r="D160" s="39" t="s">
@@ -8981,10 +8982,10 @@
       <c r="A161" s="39">
         <v>572426</v>
       </c>
-      <c r="B161" s="62">
+      <c r="B161" s="60">
         <v>45238</v>
       </c>
-      <c r="C161" s="61">
+      <c r="C161" s="60">
         <v>45176</v>
       </c>
       <c r="D161" s="39" t="s">
@@ -9007,10 +9008,10 @@
       <c r="A162" s="39">
         <v>569073</v>
       </c>
-      <c r="B162" s="62">
+      <c r="B162" s="60">
         <v>45238</v>
       </c>
-      <c r="C162" s="61">
+      <c r="C162" s="60">
         <v>45175</v>
       </c>
       <c r="D162" s="39" t="s">
@@ -9033,10 +9034,10 @@
       <c r="A163" s="39">
         <v>471652</v>
       </c>
-      <c r="B163" s="62">
+      <c r="B163" s="60">
         <v>45238</v>
       </c>
-      <c r="C163" s="61">
+      <c r="C163" s="60">
         <v>45175</v>
       </c>
       <c r="D163" s="39" t="s">
@@ -9085,19 +9086,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="63" t="s">
         <v>587</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="67"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:11" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
@@ -20596,14 +20597,14 @@
         <v>43684</v>
       </c>
       <c r="B1" s="20"/>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="66" t="s">
         <v>433</v>
       </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="68"/>
       <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -24139,14 +24140,14 @@
         <v>43427</v>
       </c>
       <c r="B1" s="20"/>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="66" t="s">
         <v>332</v>
       </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="68"/>
       <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -26017,14 +26018,14 @@
         <v>43062</v>
       </c>
       <c r="B1" s="20"/>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="66" t="s">
         <v>270</v>
       </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="68"/>
       <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -27657,17 +27658,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="69" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
